--- a/Section_Notes.xlsx
+++ b/Section_Notes.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/quinnmackay/Documents/GitHub/BICC_Holocene_LayerCount/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA850095-3700-924A-847D-7735CDD686A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7338515A-D812-E542-B31A-F5949EB3F0DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="68800" yWindow="10000" windowWidth="27780" windowHeight="18800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="45">
   <si>
     <t>EDML m</t>
   </si>
@@ -68,6 +81,93 @@
   </si>
   <si>
     <t>Converted all half layers into full at ~627, ~627.85, ~628.4</t>
+  </si>
+  <si>
+    <t>Kept 0.5 at ~630.75, 629.9, 631.35, 631.75. Removed all others. Converted ones I wasn't sure about into uncertain.</t>
+  </si>
+  <si>
+    <t>Kept 629.2ish. Dropped about 628.95.</t>
+  </si>
+  <si>
+    <t>Removed one and added two at about 633m EDML.</t>
+  </si>
+  <si>
+    <t>Kept 0.5 at about 633.7 and 633.9</t>
+  </si>
+  <si>
+    <t>Dropped 638.82 (full layer). Kept 0.5 from 638.85, 635.7, and 635.799</t>
+  </si>
+  <si>
+    <t>No NH4 data makes this section hard. Added uncertain around ~636.25</t>
+  </si>
+  <si>
+    <t>Kept 636.65 and 636.85</t>
+  </si>
+  <si>
+    <t>Added at 638.45 and 639.03</t>
+  </si>
+  <si>
+    <t>Moved some uncertain ones around. New uncertain at 639.62 and 639.68</t>
+  </si>
+  <si>
+    <t>Moved one around 639.95, kept 640.05, dropped all others.</t>
+  </si>
+  <si>
+    <t>Nothing needed.</t>
+  </si>
+  <si>
+    <t>Removed one uncertain and moved closest one to 198 just to the other side,</t>
+  </si>
+  <si>
+    <t>Kept 642.2 and 641.86. Dropped the one moved from the previous section</t>
+  </si>
+  <si>
+    <t>Moved the location of one right over the edge to the other side.</t>
+  </si>
+  <si>
+    <t>Cut just above 644.9, 644.34. 0.5 Kept: 643.75</t>
+  </si>
+  <si>
+    <t>Weak section overall. Cut 0.5 around 647.8, left rest.</t>
+  </si>
+  <si>
+    <t>Huge descrepancy in tiny area. Maybe tiepoint problem? Cut the only 0.5, ~648.45, and 648.3-648.35 (removed two, created one in the middle).</t>
+  </si>
+  <si>
+    <t>Added on EDML at 649.8</t>
+  </si>
+  <si>
+    <t>Removed ~651.27, added two on both ammonium humps</t>
+  </si>
+  <si>
+    <t>Rough section for EDML. WDC has data gap so reduced by one. Added one to EDML at barely above 652.</t>
+  </si>
+  <si>
+    <t>Cut the only 0.5 on EDML</t>
+  </si>
+  <si>
+    <t>Dropped the 0.5 around 655.25</t>
+  </si>
+  <si>
+    <t>Big discrepancy again in small area. Probably tie points. Dropped the 0.5 and the one right below 655.8</t>
+  </si>
+  <si>
+    <t>Added one at 656.34</t>
+  </si>
+  <si>
+    <t>Added on e at 656.43ish</t>
+  </si>
+  <si>
+    <t>Dropped 0.5 around 657.65</t>
+  </si>
+  <si>
+    <t>No changes needed</t>
+  </si>
+  <si>
+    <t>Dropped first 0.5 (around 657.89)</t>
+  </si>
+  <si>
+    <t>Added one at 659.09</t>
   </si>
 </sst>
 </file>
@@ -4855,6 +4955,9 @@
       <c r="G188">
         <v>2.2480796252948489</v>
       </c>
+      <c r="H188" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189">
@@ -4878,6 +4981,9 @@
       <c r="G189">
         <v>4.7666107675631793</v>
       </c>
+      <c r="H189" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190">
@@ -4901,6 +5007,9 @@
       <c r="G190">
         <v>-0.35446661642345129</v>
       </c>
+      <c r="H190" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191">
@@ -4924,6 +5033,9 @@
       <c r="G191">
         <v>1.466015189520476</v>
       </c>
+      <c r="H191" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192">
@@ -4947,8 +5059,11 @@
       <c r="G192">
         <v>2.105314685311896</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H192" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>192</v>
       </c>
@@ -4970,8 +5085,11 @@
       <c r="G193">
         <v>-1.1283223776226809</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H193" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>193</v>
       </c>
@@ -4993,8 +5111,11 @@
       <c r="G194">
         <v>2.866786448999846</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H194" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>194</v>
       </c>
@@ -5016,8 +5137,11 @@
       <c r="G195">
         <v>-3.2902756077910449</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H195" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>195</v>
       </c>
@@ -5039,8 +5163,11 @@
       <c r="G196">
         <v>1.7083657382299859</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H196" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>196</v>
       </c>
@@ -5062,8 +5189,11 @@
       <c r="G197">
         <v>3.4668421107089671</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H197" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>197</v>
       </c>
@@ -5085,8 +5215,11 @@
       <c r="G198">
         <v>0.37567975745514559</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H198" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>198</v>
       </c>
@@ -5108,8 +5241,11 @@
       <c r="G199">
         <v>2.0531097618932108</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H199" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>199</v>
       </c>
@@ -5131,8 +5267,11 @@
       <c r="G200">
         <v>1.2182556846073569</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H200" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>200</v>
       </c>
@@ -5154,8 +5293,11 @@
       <c r="G201">
         <v>-0.22978550582229221</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H201" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>201</v>
       </c>
@@ -5177,8 +5319,11 @@
       <c r="G202">
         <v>12.718484975473981</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H202" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>202</v>
       </c>
@@ -5200,8 +5345,11 @@
       <c r="G203">
         <v>2.0627696032806848</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H203" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>203</v>
       </c>
@@ -5223,8 +5371,11 @@
       <c r="G204">
         <v>2.645455720748942</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H204" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>204</v>
       </c>
@@ -5246,8 +5397,11 @@
       <c r="G205">
         <v>-1.6111401597663639</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H205" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>205</v>
       </c>
@@ -5269,8 +5423,11 @@
       <c r="G206">
         <v>-1.4564208668325589</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H206" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>206</v>
       </c>
@@ -5292,8 +5449,11 @@
       <c r="G207">
         <v>-0.96271108224573254</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H207" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>207</v>
       </c>
@@ -5315,8 +5475,11 @@
       <c r="G208">
         <v>0.97268349366822804</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H208" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>208</v>
       </c>
@@ -5338,8 +5501,11 @@
       <c r="G209">
         <v>0.71148954396267072</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H209" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>209</v>
       </c>
@@ -5361,8 +5527,11 @@
       <c r="G210">
         <v>2.0181004535388638</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H210" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>210</v>
       </c>
@@ -5384,8 +5553,11 @@
       <c r="G211">
         <v>-0.43994850056697032</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H211" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>211</v>
       </c>
@@ -5407,8 +5579,11 @@
       <c r="G212">
         <v>-1.6250735609155531</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H212" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>212</v>
       </c>
@@ -5430,8 +5605,11 @@
       <c r="G213">
         <v>1.59721342008379</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H213" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>213</v>
       </c>
@@ -5453,8 +5631,11 @@
       <c r="G214">
         <v>-0.22529531482359741</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H214" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>214</v>
       </c>
@@ -5476,8 +5657,11 @@
       <c r="G215">
         <v>-0.12685033509842469</v>
       </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H215" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>215</v>
       </c>
@@ -5499,8 +5683,11 @@
       <c r="G216">
         <v>8.0243704225722468E-2</v>
       </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H216" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>216</v>
       </c>
@@ -5522,8 +5709,11 @@
       <c r="G217">
         <v>-0.7800523777386843</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H217" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>217</v>
       </c>
@@ -5545,8 +5735,11 @@
       <c r="G218">
         <v>3.8534717647053178E-2</v>
       </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H218" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>218</v>
       </c>
@@ -5569,7 +5762,7 @@
         <v>3.0160410756943752</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>219</v>
       </c>
@@ -5592,7 +5785,7 @@
         <v>1.579531600220434</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>220</v>
       </c>
@@ -5615,7 +5808,7 @@
         <v>-0.37082856967754202</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>221</v>
       </c>
@@ -5638,7 +5831,7 @@
         <v>5.2207208612926479</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>222</v>
       </c>
@@ -5661,7 +5854,7 @@
         <v>0.67698653594379721</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>223</v>
       </c>

--- a/Section_Notes.xlsx
+++ b/Section_Notes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/quinnmackay/Documents/GitHub/BICC_Holocene_LayerCount/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7338515A-D812-E542-B31A-F5949EB3F0DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D5570A-2531-434A-ACB2-D1B6F22710CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="68800" yWindow="10000" windowWidth="27780" windowHeight="18800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="68800" yWindow="10000" windowWidth="27780" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="53">
   <si>
     <t>EDML m</t>
   </si>
@@ -168,6 +168,30 @@
   </si>
   <si>
     <t>Added one at 659.09</t>
+  </si>
+  <si>
+    <t>Dropped 0.5 at 659.6, 659.9. Moved the one in front a bit to the right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dropped 0.5 @ 662.15, Dropped full at 661.96 </t>
+  </si>
+  <si>
+    <t>No adjustments needed.</t>
+  </si>
+  <si>
+    <t>Dropped 666.9, 665.6, 666.75, 666.05, 665.75</t>
+  </si>
+  <si>
+    <t>Dropped 667.1</t>
+  </si>
+  <si>
+    <t>Dropped 670.05, 669.6</t>
+  </si>
+  <si>
+    <t>Kept the 0.5 at 670.25. Dropped rest. Also dropped a full around 671.33</t>
+  </si>
+  <si>
+    <t>Dropped 0.5 at 671.3, 671.62, 672.1, 671.9, 673.7, 675, 673.92, 672.25</t>
   </si>
 </sst>
 </file>
@@ -5761,6 +5785,9 @@
       <c r="G219">
         <v>3.0160410756943752</v>
       </c>
+      <c r="H219" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220">
@@ -5784,6 +5811,9 @@
       <c r="G220">
         <v>1.579531600220434</v>
       </c>
+      <c r="H220" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221">
@@ -5807,6 +5837,9 @@
       <c r="G221">
         <v>-0.37082856967754202</v>
       </c>
+      <c r="H221" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222">
@@ -5830,6 +5863,9 @@
       <c r="G222">
         <v>5.2207208612926479</v>
       </c>
+      <c r="H222" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223">
@@ -5853,6 +5889,9 @@
       <c r="G223">
         <v>0.67698653594379721</v>
       </c>
+      <c r="H223" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224">
@@ -5876,8 +5915,11 @@
       <c r="G224">
         <v>0.74569734326905746</v>
       </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H224" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>224</v>
       </c>
@@ -5899,8 +5941,11 @@
       <c r="G225">
         <v>1.1358195510929361</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H225" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>225</v>
       </c>
@@ -5922,8 +5967,11 @@
       <c r="G226">
         <v>6.1550338156102953</v>
       </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H226" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>226</v>
       </c>
@@ -5944,6 +5992,9 @@
       </c>
       <c r="G227">
         <v>6.3855353127328272</v>
+      </c>
+      <c r="H227" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Section_Notes.xlsx
+++ b/Section_Notes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/quinnmackay/Documents/GitHub/BICC_Holocene_LayerCount/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D5570A-2531-434A-ACB2-D1B6F22710CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{399B87EA-EA1B-524A-9736-1A538E4A7DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="68800" yWindow="10000" windowWidth="27780" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30240" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
   <si>
     <t>EDML m</t>
   </si>
@@ -193,12 +193,21 @@
   <si>
     <t>Dropped 0.5 at 671.3, 671.62, 672.1, 671.9, 673.7, 675, 673.92, 672.25</t>
   </si>
+  <si>
+    <t>Forgot some notes. Dropped one for WDC around 450.25</t>
+  </si>
+  <si>
+    <t>Forgot some notes. Removed one from EDML at about 155.08. Doing a +- with the next section</t>
+  </si>
+  <si>
+    <t>Forgot some notes. Moved a layer in WDC section just to the right.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,6 +220,13 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -259,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -267,6 +283,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -984,7 +1001,7 @@
       <c r="G16">
         <v>1.204275001852011</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1011,7 +1028,7 @@
         <v>0.33400644071389252</v>
       </c>
       <c r="H17" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -1037,7 +1054,7 @@
         <v>0.91129461239938792</v>
       </c>
       <c r="H18" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -1063,7 +1080,7 @@
         <v>-0.20977675721564989</v>
       </c>
       <c r="H19" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">

--- a/Section_Notes.xlsx
+++ b/Section_Notes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/quinnmackay/Documents/GitHub/BICC_Holocene_LayerCount/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{399B87EA-EA1B-524A-9736-1A538E4A7DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC55CACF-B0CF-9D4A-A13D-8C443C67CBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30240" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="70">
   <si>
     <t>EDML m</t>
   </si>
@@ -201,6 +201,48 @@
   </si>
   <si>
     <t>Forgot some notes. Moved a layer in WDC section just to the right.</t>
+  </si>
+  <si>
+    <t>Added two at about 166.45 and 165.8 on EDML</t>
+  </si>
+  <si>
+    <t>Removed two and mde one around 168.9 EDML</t>
+  </si>
+  <si>
+    <t>Added two uncertains in EDML</t>
+  </si>
+  <si>
+    <t>Added a uncertain to WDC at ~513. Removed three from EDML at ~173.45, ~171.53, ~170.7</t>
+  </si>
+  <si>
+    <t>~Removed 174.4 and 175.5 from EDML</t>
+  </si>
+  <si>
+    <t>Dropped 177.4, 177.7, 175.75</t>
+  </si>
+  <si>
+    <t>Dropped 178.2, 178.6, 178.9, 180.2 added 179.25 on EDML. For WDC: Added 540.05</t>
+  </si>
+  <si>
+    <t>Dropped 181.6, 182.65, 185.9, added WD at 550.2</t>
+  </si>
+  <si>
+    <t>Added two uncertain to EDML</t>
+  </si>
+  <si>
+    <t>No ajustments, but the density is weird</t>
+  </si>
+  <si>
+    <t>Added 4 uncertain layers in EDML</t>
+  </si>
+  <si>
+    <t>Added an uncertain on EDML at 196.1</t>
+  </si>
+  <si>
+    <t>Removed from EDML: 206.9, 207.7, 208.2, 209.2, 205.55</t>
+  </si>
+  <si>
+    <t>Cut 214.3, 215.7, 217.7, 219.4, 221.75, 226.6, 227.8, 227.45, 214.25</t>
   </si>
 </sst>
 </file>
@@ -1157,6 +1199,9 @@
       <c r="G22">
         <v>0.66183885558871225</v>
       </c>
+      <c r="H22" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23">
@@ -1180,6 +1225,9 @@
       <c r="G23">
         <v>-2.444860048626651</v>
       </c>
+      <c r="H23" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24">
@@ -1203,6 +1251,9 @@
       <c r="G24">
         <v>1.236809555383616</v>
       </c>
+      <c r="H24" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25">
@@ -1226,6 +1277,9 @@
       <c r="G25">
         <v>-1.785757600460784</v>
       </c>
+      <c r="H25" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26">
@@ -1249,6 +1303,9 @@
       <c r="G26">
         <v>2.541201931750265</v>
       </c>
+      <c r="H26" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27">
@@ -1272,6 +1329,9 @@
       <c r="G27">
         <v>3.430020664118274</v>
       </c>
+      <c r="H27" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28">
@@ -1295,6 +1355,9 @@
       <c r="G28">
         <v>2.2869922391673749</v>
       </c>
+      <c r="H28" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29">
@@ -1318,6 +1381,9 @@
       <c r="G29">
         <v>4.4049729084035789</v>
       </c>
+      <c r="H29" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30">
@@ -1341,6 +1407,9 @@
       <c r="G30">
         <v>4.1352058414145176</v>
       </c>
+      <c r="H30" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31">
@@ -1364,6 +1433,9 @@
       <c r="G31">
         <v>-1.9301995262371749</v>
       </c>
+      <c r="H31" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32">
@@ -1387,8 +1459,11 @@
       <c r="G32">
         <v>0.15832343397642029</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H32" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1410,8 +1485,11 @@
       <c r="G33">
         <v>-5.050825154033646</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H33" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1433,8 +1511,11 @@
       <c r="G34">
         <v>-0.24022862886658911</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1456,8 +1537,11 @@
       <c r="G35">
         <v>-2.4528321276493439</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H35" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1479,8 +1563,11 @@
       <c r="G36">
         <v>4.8216124343211959</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H36" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1502,8 +1589,11 @@
       <c r="G37">
         <v>9.4138892937894525</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H37" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1526,7 +1616,7 @@
         <v>-2.8848171641493541</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1549,7 +1639,7 @@
         <v>7.4451299948377709</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1572,7 +1662,7 @@
         <v>11.898560375443139</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1595,7 +1685,7 @@
         <v>-6.6266730271750021</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1618,7 +1708,7 @@
         <v>-3.1819961220908231</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1641,7 +1731,7 @@
         <v>0.3511194676143532</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1664,7 +1754,7 @@
         <v>2.2364046166708249</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1687,7 +1777,7 @@
         <v>4.4649839155513291</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1710,7 +1800,7 @@
         <v>-0.41843244660685741</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1733,7 +1823,7 @@
         <v>4.1499836902012248</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>

--- a/Section_Notes.xlsx
+++ b/Section_Notes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/quinnmackay/Documents/GitHub/BICC_Holocene_LayerCount/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC55CACF-B0CF-9D4A-A13D-8C443C67CBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C482CB0F-B754-0440-B7AE-195B8417AC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30240" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30240" yWindow="660" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="97">
   <si>
     <t>EDML m</t>
   </si>
@@ -243,6 +243,87 @@
   </si>
   <si>
     <t>Cut 214.3, 215.7, 217.7, 219.4, 221.75, 226.6, 227.8, 227.45, 214.25</t>
+  </si>
+  <si>
+    <t>Added one to EDML at 231.55, removed one from WDC: 718.5</t>
+  </si>
+  <si>
+    <t>From EDML: Dropped 236.25, uncertain 240.75, double peak at 238.3 and 238.35 and 237.4 and 235.6.</t>
+  </si>
+  <si>
+    <t>Kept 0.5 at 245.4, removed rest. Reduced blank spot around 242.7 by 1. Removed double peak at 244.4, peak at 246.25</t>
+  </si>
+  <si>
+    <t>Added uncertainties at 248.9, 250.25 and 249.55. I think one more but forgot which one. Removed from WD at 772.1 and 784.1 and 779.25</t>
+  </si>
+  <si>
+    <t>Added uncertainty at 254.52 and 255.95, SUPER uncertain at 255.55</t>
+  </si>
+  <si>
+    <t>Dropped 259.2, 265.5, 260.05. All were uncertain</t>
+  </si>
+  <si>
+    <t>Dropped 268.3, 267.605, 266.3, 266.405</t>
+  </si>
+  <si>
+    <t>Added uncertain at 270.3</t>
+  </si>
+  <si>
+    <t>Kept 271.4 (although very weak but wide spacing), dropped all other 0.5. Dropped 271.35. Moved the one to the left a bit to the right.</t>
+  </si>
+  <si>
+    <t>Dropped all 0.5 and 274.1</t>
+  </si>
+  <si>
+    <t>Dropped 275.85, 275.67, 275.02, 248.85</t>
+  </si>
+  <si>
+    <t>Dropped 278.45. Kept 0.5 at: 276.65, 278.4, 280.2, 280.9, 281.85, 282.8, 283.2, 235.75, 235.85, 284.45</t>
+  </si>
+  <si>
+    <t>Added uncertain EDML at 258.92</t>
+  </si>
+  <si>
+    <t>Dropped uncertain at 287.8 and 286.6</t>
+  </si>
+  <si>
+    <t>Added uncertain at 290.75</t>
+  </si>
+  <si>
+    <t>Added uncertain at 293.7 and 295.6</t>
+  </si>
+  <si>
+    <t>dropped 296.95, 301.95, 302.78, 305.75, 309.9, 308.4, 308.55, 308.15, 306.5, 299.4</t>
+  </si>
+  <si>
+    <t>Cut uncertain 311.8</t>
+  </si>
+  <si>
+    <t>Cut uncertain at 314.5. This is a really hard one (tiepoint problem?), Added new weak WDC tiepoint at about 987.2. Took two at 315.8 and made one. Removed 315.3</t>
+  </si>
+  <si>
+    <t>Dropped all uncertains except 316.65</t>
+  </si>
+  <si>
+    <t>Dropped uncertain at 319.7</t>
+  </si>
+  <si>
+    <t>Dropped uncertain at 322.05, 321.75, 322.2. Dropped full at 321.25</t>
+  </si>
+  <si>
+    <t>Dropped uncertain at 322.83, dropped full at 322.65</t>
+  </si>
+  <si>
+    <t>Removed all uncertain from EDML, added one to WDC at 1018.5 (uncertain)</t>
+  </si>
+  <si>
+    <t>Dropped full at 325.75, moved uncertain right by it. Dropped 327.25, 327.8, 328.2, 328.6, 329.05</t>
+  </si>
+  <si>
+    <t>Dropped uncertain at 329.6, 333.4, 334.45, 332.6, 333.45 (moved full just to the right of it to the left).</t>
+  </si>
+  <si>
+    <t>Another really hard one. Dropped uncertain at 337.7, dropped full at 337.85, 336.55. Added to WDC at 1057.9 and 1058.15.</t>
   </si>
 </sst>
 </file>
@@ -271,12 +352,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -317,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -326,6 +413,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1594,7 +1682,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38">
+      <c r="A38" s="4">
         <v>37</v>
       </c>
       <c r="B38">
@@ -1615,9 +1703,12 @@
       <c r="G38">
         <v>-2.8848171641493541</v>
       </c>
+      <c r="H38" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39">
+      <c r="A39" s="4">
         <v>38</v>
       </c>
       <c r="B39">
@@ -1638,9 +1729,12 @@
       <c r="G39">
         <v>7.4451299948377709</v>
       </c>
+      <c r="H39" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40">
+      <c r="A40" s="4">
         <v>39</v>
       </c>
       <c r="B40">
@@ -1661,9 +1755,12 @@
       <c r="G40">
         <v>11.898560375443139</v>
       </c>
+      <c r="H40" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41">
+      <c r="A41" s="4">
         <v>40</v>
       </c>
       <c r="B41">
@@ -1684,9 +1781,12 @@
       <c r="G41">
         <v>-6.6266730271750021</v>
       </c>
+      <c r="H41" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42">
+      <c r="A42" s="4">
         <v>41</v>
       </c>
       <c r="B42">
@@ -1707,9 +1807,12 @@
       <c r="G42">
         <v>-3.1819961220908231</v>
       </c>
+      <c r="H42" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43">
+      <c r="A43" s="4">
         <v>42</v>
       </c>
       <c r="B43">
@@ -1730,9 +1833,12 @@
       <c r="G43">
         <v>0.3511194676143532</v>
       </c>
+      <c r="H43" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44">
+      <c r="A44" s="4">
         <v>43</v>
       </c>
       <c r="B44">
@@ -1753,9 +1859,12 @@
       <c r="G44">
         <v>2.2364046166708249</v>
       </c>
+      <c r="H44" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45">
+      <c r="A45" s="4">
         <v>44</v>
       </c>
       <c r="B45">
@@ -1776,9 +1885,12 @@
       <c r="G45">
         <v>4.4649839155513291</v>
       </c>
+      <c r="H45" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46">
+      <c r="A46" s="4">
         <v>45</v>
       </c>
       <c r="B46">
@@ -1799,9 +1911,12 @@
       <c r="G46">
         <v>-0.41843244660685741</v>
       </c>
+      <c r="H46" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47">
+      <c r="A47" s="4">
         <v>46</v>
       </c>
       <c r="B47">
@@ -1822,9 +1937,12 @@
       <c r="G47">
         <v>4.1499836902012248</v>
       </c>
+      <c r="H47" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48">
+      <c r="A48" s="4">
         <v>47</v>
       </c>
       <c r="B48">
@@ -1845,9 +1963,12 @@
       <c r="G48">
         <v>4.5589685278023353</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49">
+      <c r="H48" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" s="4">
         <v>48</v>
       </c>
       <c r="B49">
@@ -1868,9 +1989,12 @@
       <c r="G49">
         <v>4.3700463696090992</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50">
+      <c r="H49" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" s="4">
         <v>49</v>
       </c>
       <c r="B50">
@@ -1891,9 +2015,12 @@
       <c r="G50">
         <v>13.967906952668731</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51">
+      <c r="H50" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" s="4">
         <v>50</v>
       </c>
       <c r="B51">
@@ -1914,9 +2041,12 @@
       <c r="G51">
         <v>-1.023754637490583</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52">
+      <c r="H51" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" s="4">
         <v>51</v>
       </c>
       <c r="B52">
@@ -1937,9 +2067,12 @@
       <c r="G52">
         <v>2.5274697908371309</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A53">
+      <c r="H52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" s="4">
         <v>52</v>
       </c>
       <c r="B53">
@@ -1960,9 +2093,12 @@
       <c r="G53">
         <v>-0.52176357120879402</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54">
+      <c r="H53" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54" s="4">
         <v>53</v>
       </c>
       <c r="B54">
@@ -1983,9 +2119,12 @@
       <c r="G54">
         <v>-1.872669285487973</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55">
+      <c r="H54" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" s="4">
         <v>54</v>
       </c>
       <c r="B55">
@@ -2006,9 +2145,12 @@
       <c r="G55">
         <v>9.2227808982274837</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56">
+      <c r="H55" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" s="4">
         <v>55</v>
       </c>
       <c r="B56">
@@ -2029,9 +2171,12 @@
       <c r="G56">
         <v>1.6637510585069319</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57">
+      <c r="H56" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" s="4">
         <v>56</v>
       </c>
       <c r="B57">
@@ -2052,9 +2197,12 @@
       <c r="G57">
         <v>3.7730450430153719</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58">
+      <c r="H57" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" s="4">
         <v>57</v>
       </c>
       <c r="B58">
@@ -2075,9 +2223,12 @@
       <c r="G58">
         <v>3.4410789075500361</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59">
+      <c r="H58" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" s="4">
         <v>58</v>
       </c>
       <c r="B59">
@@ -2098,9 +2249,12 @@
       <c r="G59">
         <v>1.346108227573495</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A60">
+      <c r="H59" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" s="4">
         <v>59</v>
       </c>
       <c r="B60">
@@ -2121,9 +2275,12 @@
       <c r="G60">
         <v>3.556648906223018</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A61">
+      <c r="H60" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" s="4">
         <v>60</v>
       </c>
       <c r="B61">
@@ -2144,9 +2301,12 @@
       <c r="G61">
         <v>2.381604067152693</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A62">
+      <c r="H61" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" s="4">
         <v>61</v>
       </c>
       <c r="B62">
@@ -2167,9 +2327,12 @@
       <c r="G62">
         <v>4.8965199730910172</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A63">
+      <c r="H62" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63" s="4">
         <v>62</v>
       </c>
       <c r="B63">
@@ -2190,9 +2353,12 @@
       <c r="G63">
         <v>6.2015099644941074</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A64">
+      <c r="H63" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64" s="4">
         <v>63</v>
       </c>
       <c r="B64">
@@ -2213,9 +2379,12 @@
       <c r="G64">
         <v>3.4653823279968492</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A65">
+      <c r="H64" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A65" s="4">
         <v>64</v>
       </c>
       <c r="B65">
@@ -2236,8 +2405,11 @@
       <c r="G65">
         <v>3.9983731130832889</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H65" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2260,7 +2432,7 @@
         <v>22.665157008064849</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2283,7 +2455,7 @@
         <v>12.350105362253091</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2306,7 +2478,7 @@
         <v>6.459456358135867</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2329,7 +2501,7 @@
         <v>3.2318920868747232</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2352,7 +2524,7 @@
         <v>7.6392241042103706</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2375,7 +2547,7 @@
         <v>3.4019300691097669</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2398,7 +2570,7 @@
         <v>-6.3959376855564187E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2421,7 +2593,7 @@
         <v>2.9747550431557102</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2444,7 +2616,7 @@
         <v>7.7548566821724307</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -2467,7 +2639,7 @@
         <v>0.30416190951928002</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2490,7 +2662,7 @@
         <v>0.78476532274635247</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2513,7 +2685,7 @@
         <v>1.3971929666286089</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -2536,7 +2708,7 @@
         <v>1.6020007209972389</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -2559,7 +2731,7 @@
         <v>9.4735812131511921</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
